--- a/utils/monday_sprint_sprint_2024-32.xlsx
+++ b/utils/monday_sprint_sprint_2024-32.xlsx
@@ -111,7 +111,7 @@
     <t>12/02/2024</t>
   </si>
   <si>
-    <t>09/05/2026</t>
+    <t>04/05/2026</t>
   </si>
   <si>
     <t>Semana 2</t>
@@ -3471,7 +3471,7 @@
         <v>43</v>
       </c>
       <c r="Q10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -3503,7 +3503,7 @@
         <v>33</v>
       </c>
       <c r="Q11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -3611,7 +3611,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>27</v>

--- a/utils/monday_sprint_sprint_2024-32.xlsx
+++ b/utils/monday_sprint_sprint_2024-32.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="193">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>22674</t>
+    <t>6269102326</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>15/03/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>26/03/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Março</t>
   </si>
   <si>
-    <t>24556</t>
+    <t>6269120594</t>
   </si>
   <si>
     <t>Controle de Período Firme - Inconsistencias</t>
@@ -111,6 +111,9 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>24/03/2024</t>
+  </si>
+  <si>
     <t>24540</t>
   </si>
   <si>
@@ -132,7 +135,7 @@
     <t>04/05/2026</t>
   </si>
   <si>
-    <t>25225</t>
+    <t>6306103615</t>
   </si>
   <si>
     <t>Indicador de origem do apontamento UPR</t>
@@ -141,19 +144,25 @@
     <t>21/03/2024</t>
   </si>
   <si>
-    <t>25079</t>
+    <t>20/03/2024</t>
+  </si>
+  <si>
+    <t>6268852357</t>
   </si>
   <si>
     <t>Relatórios para fechamento de estoques de peças: em processo e depósito</t>
   </si>
   <si>
-    <t>21782</t>
+    <t>27/03/2024</t>
+  </si>
+  <si>
+    <t>6269139883</t>
   </si>
   <si>
     <t>Diferença - Estoque Processo</t>
   </si>
   <si>
-    <t>24841</t>
+    <t>6175224328</t>
   </si>
   <si>
     <t>Aplicação de Estoque Total</t>
@@ -162,22 +171,25 @@
     <t>01/03/2024</t>
   </si>
   <si>
+    <t>31/03/2024</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
-    <t>25024</t>
+    <t>6268928236</t>
   </si>
   <si>
     <t>Criar aplicação Sense de cálculo de IROG para a linha Ajustagem UPR</t>
   </si>
   <si>
-    <t>24901</t>
+    <t>6176758614</t>
   </si>
   <si>
     <t>Sistema de Previsão de Vendas (Ofertas e Forecast) Definição de Escopo</t>
   </si>
   <si>
-    <t>24270</t>
+    <t>5990560934</t>
   </si>
   <si>
     <t>ALTERAÇÃO PARCELAS SISTEMA INVOICE - ATUALIZAÇÃO PARCELAS</t>
@@ -189,16 +201,22 @@
     <t>Fevereiro</t>
   </si>
   <si>
+    <t>6277336495</t>
+  </si>
+  <si>
     <t>ALTERAÇÃO PARCELAS SISTEMA INVOICE  - TIPO DE PAGAMENTO</t>
   </si>
   <si>
     <t>18/03/2024</t>
   </si>
   <si>
+    <t>6277346870</t>
+  </si>
+  <si>
     <t>ALTERAÇÃO PARCELAS SISTEMA INVOICE  - JANELA DE PAGTO/CLIENTE</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>6175371598</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -207,163 +225,172 @@
     <t>AJUSTES CONDIÇÃO DE PAGAMENTO OFERTA / CPC - Estrutura de pagamentos CPC</t>
   </si>
   <si>
-    <t>24998</t>
+    <t>6268960800</t>
   </si>
   <si>
     <t>PROBLEMA NO CPP ABA DESMOLDAGEM</t>
   </si>
   <si>
-    <t>25027</t>
+    <t>6268907878</t>
   </si>
   <si>
     <t>Inclusão na Planilha MPS</t>
   </si>
   <si>
-    <t>25140</t>
+    <t>6269864786</t>
   </si>
   <si>
     <t>INCLUSÃO CAMPO 3D DE CONJUNTO NO FORMULÁRIO DE "Dados Desenho 3D" DO SETOR 5</t>
   </si>
   <si>
-    <t>25125</t>
+    <t>6268740595</t>
   </si>
   <si>
     <t>Informação de Comissão - Rel NF Despachada</t>
   </si>
   <si>
-    <t>25114</t>
+    <t>6268763878</t>
   </si>
   <si>
     <t>Corrigir Cálculo do Custo Médio Sucata Retorno FEV/2024</t>
   </si>
   <si>
-    <t>25046</t>
+    <t>6268862327</t>
   </si>
   <si>
     <t>Corrida não mostra peso do conjunto na consulta</t>
   </si>
   <si>
-    <t>24942</t>
+    <t>6269016009</t>
   </si>
   <si>
     <t>Divergência no Faturamento</t>
   </si>
   <si>
-    <t>24689</t>
+    <t>6175408973</t>
   </si>
   <si>
     <t>Alteração de nomenclatura</t>
   </si>
   <si>
+    <t>6431090659</t>
+  </si>
+  <si>
     <t>Alteração de nomenclatura - Não Atendido</t>
   </si>
   <si>
     <t>10/04/2024</t>
   </si>
   <si>
+    <t>09/04/2024</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
     <t>Abril</t>
   </si>
   <si>
-    <t>24686</t>
+    <t>6175417163</t>
   </si>
   <si>
     <t>Alterar texto</t>
   </si>
   <si>
-    <t>24855</t>
+    <t>6175190940</t>
   </si>
   <si>
     <t>Melhoria do sistema de registro</t>
   </si>
   <si>
-    <t>25091</t>
+    <t>6268810004</t>
   </si>
   <si>
     <t>Melhoria no portal de pendencias</t>
   </si>
   <si>
-    <t>25028</t>
+    <t>6268883952</t>
   </si>
   <si>
     <t>Relatório de PIS e COFINS</t>
   </si>
   <si>
-    <t>25019</t>
+    <t>6268944189</t>
   </si>
   <si>
     <t>CÓPIA COMPLETA DE CPP</t>
   </si>
   <si>
-    <t>24935</t>
+    <t>6269024442</t>
   </si>
   <si>
     <t>Alteração de baixa de sics_distribuição de informações</t>
   </si>
   <si>
-    <t>24932</t>
+    <t>6269033595</t>
   </si>
   <si>
     <t>[NIMBI] Chamado para adição de API para integração impostos</t>
   </si>
   <si>
-    <t>24927</t>
+    <t>6269054726</t>
   </si>
   <si>
     <t>Alteração de baixa de sics</t>
   </si>
   <si>
-    <t>24289</t>
+    <t>6269093141</t>
   </si>
   <si>
     <t>Melhorias e Alterações - Controle na moldagem + planilha MPS</t>
   </si>
   <si>
-    <t>25148</t>
+    <t>6269344321</t>
   </si>
   <si>
     <t>MODELO CLIENTE</t>
   </si>
   <si>
-    <t>25144</t>
+    <t>6269377643</t>
   </si>
   <si>
     <t>Eliminar os testes de inventário aberto</t>
   </si>
   <si>
-    <t>25143</t>
+    <t>19/03/2024</t>
+  </si>
+  <si>
+    <t>6269394790</t>
   </si>
   <si>
     <t>Romaneios que estão no BOX “0”</t>
   </si>
   <si>
-    <t>22873</t>
+    <t>6269664320</t>
   </si>
   <si>
     <t>Baixa Saldo EPIS</t>
   </si>
   <si>
-    <t>24815</t>
+    <t>6269702354</t>
   </si>
   <si>
     <t>Valorização e Movimentação dos Estoques de Produtos - II Relatório de Faturamento</t>
   </si>
   <si>
-    <t>24816</t>
+    <t>6269718879</t>
   </si>
   <si>
     <t>Valorização e Movimentação dos Estoques de Produtos - IV Relatório Saída do Corte de Cana</t>
   </si>
   <si>
-    <t>25117</t>
+    <t>6269915221</t>
   </si>
   <si>
     <t>Relatório de Lançamento de notas por usuário</t>
   </si>
   <si>
-    <t>24544</t>
+    <t>6080638514</t>
   </si>
   <si>
     <t>Plano de ação WMS - Cadastro de Operadores</t>
@@ -372,25 +399,25 @@
     <t>16/02/2024</t>
   </si>
   <si>
-    <t>24543</t>
+    <t>6080649570</t>
   </si>
   <si>
     <t>Plano de Ação WMS - Coleta e entrega</t>
   </si>
   <si>
-    <t>24663</t>
+    <t>6175500380</t>
   </si>
   <si>
     <t>Inclusão de sequencia - Contentor</t>
   </si>
   <si>
-    <t>24349</t>
+    <t>5989981568</t>
   </si>
   <si>
     <t>Ajuste de dupla checagem de composição química - Spectro</t>
   </si>
   <si>
-    <t>24640</t>
+    <t>6093377975</t>
   </si>
   <si>
     <t>Extração apontamentos de solda - SENSE + QG</t>
@@ -399,7 +426,7 @@
     <t>19/02/2024</t>
   </si>
   <si>
-    <t>24445</t>
+    <t>6034716958</t>
   </si>
   <si>
     <t>PN# DAS INVOICES DA KOMATSU</t>
@@ -408,13 +435,13 @@
     <t>09/02/2024</t>
   </si>
   <si>
-    <t>24408</t>
+    <t>6034766489</t>
   </si>
   <si>
     <t>ERRO: Sistema Apontamentos Tratamento Térmico</t>
   </si>
   <si>
-    <t>23840</t>
+    <t>5819483475</t>
   </si>
   <si>
     <t>Atualização - Recibo de Embarque - Criar interface de assinatura</t>
@@ -426,16 +453,19 @@
     <t>Janeiro</t>
   </si>
   <si>
-    <t>23876</t>
+    <t>6280188660</t>
   </si>
   <si>
     <t>Colunas "prévia" não atualiza quando sem Sequencia</t>
   </si>
   <si>
+    <t>6277181741</t>
+  </si>
+  <si>
     <t>Atualização - Recibo de Embarque - Migrar aplicação win</t>
   </si>
   <si>
-    <t>25187</t>
+    <t>6287350841</t>
   </si>
   <si>
     <t>Correção</t>
@@ -444,25 +474,19 @@
     <t>Erro apontamento de ajustagem</t>
   </si>
   <si>
-    <t>19/03/2024</t>
-  </si>
-  <si>
-    <t>25177</t>
+    <t>6291359952</t>
   </si>
   <si>
     <t>Tela requisição de materiais</t>
   </si>
   <si>
-    <t>21601</t>
+    <t>6294167153</t>
   </si>
   <si>
     <t>GERAÇÃO DE ROMANEIO - EXPEDIÇÃO</t>
   </si>
   <si>
-    <t>20/03/2024</t>
-  </si>
-  <si>
-    <t>24417</t>
+    <t>6034758455</t>
   </si>
   <si>
     <t>ALTERAÇÃO FOLLOW CLIENTE NO SISTEMA DE INVOICE</t>
@@ -474,7 +498,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-32</t>
+    <t>Jan/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -546,7 +570,13 @@
     <t>Fazendo</t>
   </si>
   <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
     <t>Não definida</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -1122,7 +1152,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1139,7 +1169,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1148,28 +1178,28 @@
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1186,7 +1216,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1198,10 +1228,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1213,10 +1243,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1233,7 +1263,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1245,10 +1275,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1263,7 +1293,7 @@
         <v>23</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1280,7 +1310,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1292,10 +1322,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>31</v>
@@ -1310,7 +1340,7 @@
         <v>23</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1327,7 +1357,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1339,10 +1369,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1354,10 +1384,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1366,7 +1396,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1374,7 +1404,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1386,10 +1416,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1404,7 +1434,7 @@
         <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1421,7 +1451,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1433,10 +1463,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>31</v>
@@ -1448,10 +1478,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1460,7 +1490,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -1468,7 +1498,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1480,10 +1510,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>31</v>
@@ -1495,10 +1525,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1507,15 +1537,15 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1527,10 +1557,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>31</v>
@@ -1542,10 +1572,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1562,7 +1592,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1574,10 +1604,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>31</v>
@@ -1589,10 +1619,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1609,22 +1639,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>31</v>
@@ -1636,10 +1666,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1648,7 +1678,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1656,7 +1686,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1668,10 +1698,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1686,7 +1716,7 @@
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1703,7 +1733,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1715,10 +1745,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1733,7 +1763,7 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1750,7 +1780,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1762,10 +1792,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1780,7 +1810,7 @@
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1797,7 +1827,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1809,10 +1839,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1827,7 +1857,7 @@
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1844,7 +1874,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1856,10 +1886,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1874,7 +1904,7 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1891,7 +1921,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1903,10 +1933,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1921,7 +1951,7 @@
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1938,7 +1968,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1950,10 +1980,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1968,7 +1998,7 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1985,7 +2015,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1997,10 +2027,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2012,10 +2042,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2024,7 +2054,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -2032,7 +2062,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2044,10 +2074,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2059,10 +2089,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2071,15 +2101,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2091,10 +2121,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2106,10 +2136,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2118,7 +2148,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2126,7 +2156,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2138,10 +2168,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2153,10 +2183,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2165,7 +2195,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>28</v>
@@ -2173,7 +2203,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2185,10 +2215,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2203,7 +2233,7 @@
         <v>23</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2220,7 +2250,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2232,10 +2262,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2267,7 +2297,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2279,10 +2309,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2297,7 +2327,7 @@
         <v>23</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2314,7 +2344,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2326,10 +2356,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2344,7 +2374,7 @@
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2361,7 +2391,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2373,10 +2403,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2391,7 +2421,7 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2408,7 +2438,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2420,10 +2450,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2438,7 +2468,7 @@
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2455,7 +2485,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2467,10 +2497,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>31</v>
@@ -2502,7 +2532,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2514,10 +2544,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2532,7 +2562,7 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2549,7 +2579,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2561,10 +2591,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2579,7 +2609,7 @@
         <v>23</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2596,7 +2626,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2608,10 +2638,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2626,7 +2656,7 @@
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2643,7 +2673,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2655,10 +2685,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>31</v>
@@ -2673,7 +2703,7 @@
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2690,7 +2720,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2702,10 +2732,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2720,7 +2750,7 @@
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2737,7 +2767,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2749,10 +2779,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2767,7 +2797,7 @@
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2784,7 +2814,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2796,10 +2826,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2831,7 +2861,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2843,10 +2873,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2858,10 +2888,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2873,12 +2903,12 @@
         <v>27</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2890,10 +2920,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2905,10 +2935,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2920,12 +2950,12 @@
         <v>27</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2937,10 +2967,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2952,10 +2982,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2964,7 +2994,7 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -2972,7 +3002,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2984,10 +3014,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>31</v>
@@ -2999,10 +3029,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3011,15 +3041,15 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3031,10 +3061,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>31</v>
@@ -3046,10 +3076,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3061,12 +3091,12 @@
         <v>27</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3078,10 +3108,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3093,10 +3123,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3105,15 +3135,15 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3125,10 +3155,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3140,10 +3170,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3152,15 +3182,15 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3172,10 +3202,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3187,10 +3217,10 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3199,15 +3229,15 @@
         <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3219,10 +3249,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3234,7 +3264,7 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>24</v>
@@ -3254,7 +3284,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3266,10 +3296,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3281,7 +3311,7 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>24</v>
@@ -3301,22 +3331,22 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>31</v>
@@ -3328,10 +3358,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3348,7 +3378,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3360,10 +3390,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3375,10 +3405,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3395,22 +3425,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>31</v>
@@ -3422,10 +3452,10 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3442,7 +3472,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3454,10 +3484,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3469,10 +3499,10 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
@@ -3481,10 +3511,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -3500,23 +3530,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3524,16 +3554,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3544,7 +3574,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>781</v>
+        <v>33.48</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3552,7 +3582,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3565,7 +3595,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3573,7 +3603,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3604,12 +3634,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B2">
         <v>52</v>
@@ -3623,7 +3653,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>781</v>
+        <v>33.48</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3633,25 +3663,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3668,13 +3698,13 @@
         <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3686,15 +3716,15 @@
         <v>52</v>
       </c>
       <c r="P10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Q10">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -3712,21 +3742,21 @@
         <v>52</v>
       </c>
       <c r="M11" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3738,13 +3768,13 @@
         <v>39</v>
       </c>
       <c r="J12" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3753,40 +3783,52 @@
         <v>27</v>
       </c>
       <c r="Q12">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="P13" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
+      <c r="P14" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q14">
+        <v>12</v>
+      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3794,7 +3836,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3802,7 +3844,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3810,10 +3852,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3821,7 +3863,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3829,142 +3871,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>766</v>
+        <v>833</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
